--- a/extenbooks/S1506_extenbook.xlsx
+++ b/extenbooks/S1506_extenbook.xlsx
@@ -5433,7 +5433,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: ingested</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
@@ -6267,11 +6267,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6294,64 +6294,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Chapter 15 series S1506</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>chapter</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>extenbook_published</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>["3_research", "4_adequacy", "5_ingestion", "6_extension", "7_replication", "8_output"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{"research_json": "Technical/research/S1506_research.json", "adequacy_report": "Technical/docs/chapters/CH15_ADEQUACY_REPORT.json", "dpr": "Technical/docs/series/S1506_DPR.md", "epr": "Technical/docs/series/S1506_EPR.md", "loader": "Technical/code/L01_loaders/L01_S1506_load.py", "processor": "Technical/code/P02_processors/P02_S1506_construct.py", "validator": "Technical/code/V03_validators/V03_S1506_validate.py", "processed": "Technical/data/processed/S1506.parquet", "chopped_csv": "Technical/chopped/S1506.csv", "extenbook_xlsx": "Technical/extenbooks/S1506_extenbook.xlsx"}</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S1506_extenbook.xlsx
+++ b/extenbooks/S1506_extenbook.xlsx
@@ -1638,7 +1638,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -3133,7 +3133,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -3363,7 +3363,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -3478,7 +3478,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -3823,7 +3823,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -4053,7 +4053,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -4168,7 +4168,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -4513,7 +4513,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -4628,7 +4628,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4743,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -4973,7 +4973,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -5419,7 +5419,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>**Phase**: 5 (Ingestion)</t>
+          <t>**Pipeline stage**: Ingestion</t>
         </is>
       </c>
     </row>
@@ -5461,7 +5461,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>**Author**: opus-subagent-fanout-ch15</t>
+          <t>**Author**: RSCD replication pipeline (automated)</t>
         </is>
       </c>
     </row>
@@ -5645,7 +5645,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>- **CD legacy IDs**: `S085`, `S088` predecessors</t>
+          <t>- **Predecessor-build IDs**: `S085`, `S088` predecessors</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5709,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>**Phase**: 6 (Extension)</t>
+          <t>**Pipeline stage**: Extension</t>
         </is>
       </c>
     </row>
@@ -5737,7 +5737,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>**Author**: opus-subagent-fanout-ch15</t>
+          <t>**Author**: RSCD replication pipeline (automated)</t>
         </is>
       </c>
     </row>
@@ -5767,7 +5767,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>S1506 is, by design, a closed historical view of S1505: the pre-Volcker era ends in 1981. Extending it forward would defeat its analytical purpose. Per the Anu Framework, `derived_subperiod` series that are closed inherit `extension_status: not_applicable_closed_subperiod` and emit no extension subseries.</t>
+          <t>S1506 is, by design, a closed historical view of S1505: the pre-Volcker era ends in 1981. Extending it forward would defeat its analytical purpose. Per this project's conventions, `derived_subperiod` series that are closed inherit `extension_status: not_applicable_closed_subperiod` and emit no extension subseries.</t>
         </is>
       </c>
     </row>
@@ -6252,7 +6252,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-05-18T22:14:08.288266+00:00</t>
+          <t>2026-07-10T14:18:45.433885+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S1506_extenbook.xlsx
+++ b/extenbooks/S1506_extenbook.xlsx
@@ -6252,7 +6252,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-10T14:18:45.433885+00:00</t>
+          <t>2026-07-11T03:44:23.439610+00:00</t>
         </is>
       </c>
     </row>
@@ -6267,11 +6267,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6294,6 +6294,150 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SHAIKH_2016_APPENDIX_15_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>derived_subperiod</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>book_period_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pipeline_consistent</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "Faithful derived sub-period of S1505 covering 1948-1981, replicating book figure 15.8 (pre-Volcker/pre-neoliberal regime). Construction-relevant: the chapter splits the postwar Phillips relationship at the structural break to show the classical curve's linearity in this era. Deterministic slice of S1505, no independent fetch; same source map. Per-subseries units split (sigma-prime normalized).", "date": "2026-06-11"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S1506_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S1506_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>time_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>per_subseries</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
